--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121285639</v>
+        <v>121285634</v>
       </c>
       <c r="B6" t="n">
-        <v>95618</v>
+        <v>97025</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,25 +1123,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518070</v>
+        <v>518077</v>
       </c>
       <c r="R6" t="n">
-        <v>6709176</v>
+        <v>6709154</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121285634</v>
+        <v>121285639</v>
       </c>
       <c r="B7" t="n">
-        <v>97025</v>
+        <v>95618</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,25 +1230,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518077</v>
+        <v>518070</v>
       </c>
       <c r="R7" t="n">
-        <v>6709154</v>
+        <v>6709176</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121285638</v>
+        <v>121285633</v>
       </c>
       <c r="B2" t="n">
-        <v>95618</v>
+        <v>97035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518072</v>
+        <v>518077</v>
       </c>
       <c r="R2" t="n">
-        <v>6709135</v>
+        <v>6709191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285633</v>
+        <v>121285631</v>
       </c>
       <c r="B3" t="n">
-        <v>97025</v>
+        <v>91093</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518077</v>
+        <v>518058</v>
       </c>
       <c r="R3" t="n">
-        <v>6709191</v>
+        <v>6709102</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285631</v>
+        <v>121285638</v>
       </c>
       <c r="B4" t="n">
-        <v>91083</v>
+        <v>95628</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518058</v>
+        <v>518072</v>
       </c>
       <c r="R4" t="n">
-        <v>6709102</v>
+        <v>6709135</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285619</v>
+        <v>121285634</v>
       </c>
       <c r="B5" t="n">
-        <v>91295</v>
+        <v>97035</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,41 +1008,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>483</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518028</v>
+        <v>518077</v>
       </c>
       <c r="R5" t="n">
-        <v>6709071</v>
+        <v>6709154</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,11 +1084,6 @@
       </c>
       <c r="AE5" t="b">
         <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1111,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121285634</v>
+        <v>121285639</v>
       </c>
       <c r="B6" t="n">
-        <v>97025</v>
+        <v>95628</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518077</v>
+        <v>518070</v>
       </c>
       <c r="R6" t="n">
-        <v>6709154</v>
+        <v>6709176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121285639</v>
+        <v>121285619</v>
       </c>
       <c r="B7" t="n">
-        <v>95618</v>
+        <v>91305</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,38 +1222,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>483</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518070</v>
+        <v>518028</v>
       </c>
       <c r="R7" t="n">
-        <v>6709176</v>
+        <v>6709071</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,6 +1301,11 @@
       </c>
       <c r="AE7" t="b">
         <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121285620</v>
+        <v>121285632</v>
       </c>
       <c r="B8" t="n">
-        <v>4766</v>
+        <v>5189</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517983</v>
+        <v>518073</v>
       </c>
       <c r="R8" t="n">
-        <v>6709000</v>
+        <v>6709135</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121285632</v>
+        <v>121285620</v>
       </c>
       <c r="B9" t="n">
-        <v>5189</v>
+        <v>4766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518073</v>
+        <v>517983</v>
       </c>
       <c r="R9" t="n">
-        <v>6709135</v>
+        <v>6709000</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -775,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285631</v>
+        <v>121285638</v>
       </c>
       <c r="B3" t="n">
-        <v>91093</v>
+        <v>95628</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518058</v>
+        <v>518072</v>
       </c>
       <c r="R3" t="n">
-        <v>6709102</v>
+        <v>6709135</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,17 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285638</v>
+        <v>121285619</v>
       </c>
       <c r="B4" t="n">
-        <v>95628</v>
+        <v>91305</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +901,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>483</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518072</v>
+        <v>518028</v>
       </c>
       <c r="R4" t="n">
-        <v>6709135</v>
+        <v>6709071</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,6 +980,11 @@
       </c>
       <c r="AE4" t="b">
         <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -996,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285634</v>
+        <v>121285631</v>
       </c>
       <c r="B5" t="n">
-        <v>97035</v>
+        <v>91093</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518077</v>
+        <v>518058</v>
       </c>
       <c r="R5" t="n">
-        <v>6709154</v>
+        <v>6709102</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121285639</v>
+        <v>121285634</v>
       </c>
       <c r="B6" t="n">
-        <v>95628</v>
+        <v>97035</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1123,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518070</v>
+        <v>518077</v>
       </c>
       <c r="R6" t="n">
-        <v>6709176</v>
+        <v>6709154</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,17 +1211,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121285619</v>
+        <v>121285639</v>
       </c>
       <c r="B7" t="n">
-        <v>91305</v>
+        <v>95628</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,41 +1230,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>483</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518028</v>
+        <v>518070</v>
       </c>
       <c r="R7" t="n">
-        <v>6709071</v>
+        <v>6709176</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,11 +1307,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121285632</v>
+        <v>121285620</v>
       </c>
       <c r="B8" t="n">
-        <v>5189</v>
+        <v>4766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518073</v>
+        <v>517983</v>
       </c>
       <c r="R8" t="n">
-        <v>6709135</v>
+        <v>6709000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121285620</v>
+        <v>121285632</v>
       </c>
       <c r="B9" t="n">
-        <v>4766</v>
+        <v>5189</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517983</v>
+        <v>518073</v>
       </c>
       <c r="R9" t="n">
-        <v>6709000</v>
+        <v>6709135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121285633</v>
+        <v>121285619</v>
       </c>
       <c r="B2" t="n">
-        <v>97035</v>
+        <v>91317</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>483</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518077</v>
+        <v>518028</v>
       </c>
       <c r="R2" t="n">
-        <v>6709191</v>
+        <v>6709071</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,6 +767,11 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -775,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285638</v>
+        <v>121285631</v>
       </c>
       <c r="B3" t="n">
-        <v>95628</v>
+        <v>91105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518072</v>
+        <v>518058</v>
       </c>
       <c r="R3" t="n">
-        <v>6709135</v>
+        <v>6709102</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,17 +890,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285619</v>
+        <v>121285633</v>
       </c>
       <c r="B4" t="n">
-        <v>91305</v>
+        <v>97048</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,41 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>483</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518028</v>
+        <v>518077</v>
       </c>
       <c r="R4" t="n">
-        <v>6709071</v>
+        <v>6709191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,11 +985,6 @@
       </c>
       <c r="AE4" t="b">
         <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285631</v>
+        <v>121285634</v>
       </c>
       <c r="B5" t="n">
-        <v>91093</v>
+        <v>97048</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518058</v>
+        <v>518077</v>
       </c>
       <c r="R5" t="n">
-        <v>6709102</v>
+        <v>6709154</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121285634</v>
+        <v>121285638</v>
       </c>
       <c r="B6" t="n">
-        <v>97035</v>
+        <v>95641</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,25 +1123,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518077</v>
+        <v>518072</v>
       </c>
       <c r="R6" t="n">
-        <v>6709154</v>
+        <v>6709135</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1221,7 +1221,7 @@
         <v>121285639</v>
       </c>
       <c r="B7" t="n">
-        <v>95628</v>
+        <v>95641</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121285620</v>
+        <v>121285630</v>
       </c>
       <c r="B8" t="n">
-        <v>4766</v>
+        <v>8421</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517983</v>
+        <v>518018</v>
       </c>
       <c r="R8" t="n">
-        <v>6709000</v>
+        <v>6709006</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1552,17 +1552,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285630</v>
+        <v>121285620</v>
       </c>
       <c r="B10" t="n">
-        <v>8421</v>
+        <v>4766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518018</v>
+        <v>517983</v>
       </c>
       <c r="R10" t="n">
-        <v>6709006</v>
+        <v>6709000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121285619</v>
+        <v>121285634</v>
       </c>
       <c r="B2" t="n">
-        <v>91317</v>
+        <v>97049</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>483</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518028</v>
+        <v>518077</v>
       </c>
       <c r="R2" t="n">
-        <v>6709071</v>
+        <v>6709154</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,11 +763,6 @@
       </c>
       <c r="AE2" t="b">
         <v>0</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -790,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285631</v>
+        <v>121285619</v>
       </c>
       <c r="B3" t="n">
-        <v>91105</v>
+        <v>91318</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>483</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518058</v>
+        <v>518028</v>
       </c>
       <c r="R3" t="n">
-        <v>6709102</v>
+        <v>6709071</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,6 +873,11 @@
       </c>
       <c r="AE3" t="b">
         <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>121285633</v>
       </c>
       <c r="B4" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285634</v>
+        <v>121285639</v>
       </c>
       <c r="B5" t="n">
-        <v>97048</v>
+        <v>95642</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,25 +1016,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518077</v>
+        <v>518070</v>
       </c>
       <c r="R5" t="n">
-        <v>6709154</v>
+        <v>6709176</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121285638</v>
+        <v>121285631</v>
       </c>
       <c r="B6" t="n">
-        <v>95641</v>
+        <v>91106</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,25 +1123,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518072</v>
+        <v>518058</v>
       </c>
       <c r="R6" t="n">
-        <v>6709135</v>
+        <v>6709102</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121285639</v>
+        <v>121285638</v>
       </c>
       <c r="B7" t="n">
-        <v>95641</v>
+        <v>95642</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518070</v>
+        <v>518072</v>
       </c>
       <c r="R7" t="n">
-        <v>6709176</v>
+        <v>6709135</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121285634</v>
+        <v>121285639</v>
       </c>
       <c r="B2" t="n">
-        <v>97049</v>
+        <v>95645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518077</v>
+        <v>518070</v>
       </c>
       <c r="R2" t="n">
-        <v>6709154</v>
+        <v>6709176</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285619</v>
+        <v>121285633</v>
       </c>
       <c r="B3" t="n">
-        <v>91318</v>
+        <v>97052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,41 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>483</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518028</v>
+        <v>518077</v>
       </c>
       <c r="R3" t="n">
-        <v>6709071</v>
+        <v>6709191</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,11 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,17 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285633</v>
+        <v>121285638</v>
       </c>
       <c r="B4" t="n">
-        <v>97049</v>
+        <v>95645</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518077</v>
+        <v>518072</v>
       </c>
       <c r="R4" t="n">
-        <v>6709191</v>
+        <v>6709135</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,17 +989,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285639</v>
+        <v>121285619</v>
       </c>
       <c r="B5" t="n">
-        <v>95642</v>
+        <v>91321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,38 +1008,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>483</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518070</v>
+        <v>518028</v>
       </c>
       <c r="R5" t="n">
-        <v>6709176</v>
+        <v>6709071</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,6 +1088,11 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
         <v>121285631</v>
       </c>
       <c r="B6" t="n">
-        <v>91106</v>
+        <v>91109</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,17 +1211,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121285638</v>
+        <v>121285634</v>
       </c>
       <c r="B7" t="n">
-        <v>95642</v>
+        <v>97052</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,25 +1230,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518072</v>
+        <v>518077</v>
       </c>
       <c r="R7" t="n">
-        <v>6709135</v>
+        <v>6709154</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121285630</v>
+        <v>121285632</v>
       </c>
       <c r="B8" t="n">
-        <v>8421</v>
+        <v>5192</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518018</v>
+        <v>518073</v>
       </c>
       <c r="R8" t="n">
-        <v>6709006</v>
+        <v>6709135</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121285632</v>
+        <v>121285630</v>
       </c>
       <c r="B9" t="n">
-        <v>5189</v>
+        <v>8424</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518073</v>
+        <v>518018</v>
       </c>
       <c r="R9" t="n">
-        <v>6709135</v>
+        <v>6709006</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
         <v>121285620</v>
       </c>
       <c r="B10" t="n">
-        <v>4766</v>
+        <v>4769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121285639</v>
+        <v>121285631</v>
       </c>
       <c r="B2" t="n">
-        <v>95645</v>
+        <v>91109</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518070</v>
+        <v>518058</v>
       </c>
       <c r="R2" t="n">
-        <v>6709176</v>
+        <v>6709102</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -882,14 +882,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285638</v>
+        <v>121285639</v>
       </c>
       <c r="B4" t="n">
         <v>95645</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518072</v>
+        <v>518070</v>
       </c>
       <c r="R4" t="n">
-        <v>6709135</v>
+        <v>6709176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,17 +989,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285619</v>
+        <v>121285638</v>
       </c>
       <c r="B5" t="n">
-        <v>91321</v>
+        <v>95645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,41 +1008,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>483</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518028</v>
+        <v>518072</v>
       </c>
       <c r="R5" t="n">
-        <v>6709071</v>
+        <v>6709135</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,11 +1085,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,17 +1096,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121285631</v>
+        <v>121285619</v>
       </c>
       <c r="B6" t="n">
-        <v>91109</v>
+        <v>91321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,38 +1115,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>483</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518058</v>
+        <v>518028</v>
       </c>
       <c r="R6" t="n">
-        <v>6709102</v>
+        <v>6709071</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,6 +1195,11 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121285632</v>
+        <v>121285620</v>
       </c>
       <c r="B8" t="n">
-        <v>5192</v>
+        <v>4769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518073</v>
+        <v>517983</v>
       </c>
       <c r="R8" t="n">
-        <v>6709135</v>
+        <v>6709000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1552,17 +1552,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285620</v>
+        <v>121285632</v>
       </c>
       <c r="B10" t="n">
-        <v>4769</v>
+        <v>5192</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517983</v>
+        <v>518073</v>
       </c>
       <c r="R10" t="n">
-        <v>6709000</v>
+        <v>6709135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121285631</v>
+        <v>121285634</v>
       </c>
       <c r="B2" t="n">
-        <v>91109</v>
+        <v>97058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518058</v>
+        <v>518077</v>
       </c>
       <c r="R2" t="n">
-        <v>6709102</v>
+        <v>6709154</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285633</v>
+        <v>121285631</v>
       </c>
       <c r="B3" t="n">
-        <v>97052</v>
+        <v>91115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518077</v>
+        <v>518058</v>
       </c>
       <c r="R3" t="n">
-        <v>6709191</v>
+        <v>6709102</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285639</v>
+        <v>121285633</v>
       </c>
       <c r="B4" t="n">
-        <v>95645</v>
+        <v>97058</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518070</v>
+        <v>518077</v>
       </c>
       <c r="R4" t="n">
-        <v>6709176</v>
+        <v>6709191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285638</v>
+        <v>121285619</v>
       </c>
       <c r="B5" t="n">
-        <v>95645</v>
+        <v>91327</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,38 +1008,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>483</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518072</v>
+        <v>518028</v>
       </c>
       <c r="R5" t="n">
-        <v>6709135</v>
+        <v>6709071</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,6 +1087,11 @@
       </c>
       <c r="AE5" t="b">
         <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1103,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121285619</v>
+        <v>121285639</v>
       </c>
       <c r="B6" t="n">
-        <v>91321</v>
+        <v>95651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,41 +1123,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>483</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518028</v>
+        <v>518070</v>
       </c>
       <c r="R6" t="n">
-        <v>6709071</v>
+        <v>6709176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,11 +1199,6 @@
       </c>
       <c r="AE6" t="b">
         <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121285634</v>
+        <v>121285638</v>
       </c>
       <c r="B7" t="n">
-        <v>97052</v>
+        <v>95651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,25 +1230,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518077</v>
+        <v>518072</v>
       </c>
       <c r="R7" t="n">
-        <v>6709154</v>
+        <v>6709135</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121285634</v>
+        <v>121285631</v>
       </c>
       <c r="B2" t="n">
-        <v>97058</v>
+        <v>91116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518077</v>
+        <v>518058</v>
       </c>
       <c r="R2" t="n">
-        <v>6709154</v>
+        <v>6709102</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285631</v>
+        <v>121285639</v>
       </c>
       <c r="B3" t="n">
-        <v>91115</v>
+        <v>95652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518058</v>
+        <v>518070</v>
       </c>
       <c r="R3" t="n">
-        <v>6709102</v>
+        <v>6709176</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285633</v>
+        <v>121285638</v>
       </c>
       <c r="B4" t="n">
-        <v>97058</v>
+        <v>95652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518077</v>
+        <v>518072</v>
       </c>
       <c r="R4" t="n">
-        <v>6709191</v>
+        <v>6709135</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>121285619</v>
       </c>
       <c r="B5" t="n">
-        <v>91327</v>
+        <v>91328</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121285639</v>
+        <v>121285633</v>
       </c>
       <c r="B6" t="n">
-        <v>95651</v>
+        <v>97059</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,25 +1123,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518070</v>
+        <v>518077</v>
       </c>
       <c r="R6" t="n">
-        <v>6709176</v>
+        <v>6709191</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121285638</v>
+        <v>121285634</v>
       </c>
       <c r="B7" t="n">
-        <v>95651</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,25 +1230,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518072</v>
+        <v>518077</v>
       </c>
       <c r="R7" t="n">
-        <v>6709135</v>
+        <v>6709154</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121285620</v>
+        <v>121285632</v>
       </c>
       <c r="B8" t="n">
-        <v>4769</v>
+        <v>5192</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517983</v>
+        <v>518073</v>
       </c>
       <c r="R8" t="n">
-        <v>6709000</v>
+        <v>6709135</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285632</v>
+        <v>121285620</v>
       </c>
       <c r="B10" t="n">
-        <v>5192</v>
+        <v>4769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518073</v>
+        <v>517983</v>
       </c>
       <c r="R10" t="n">
-        <v>6709135</v>
+        <v>6709000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285639</v>
+        <v>121285619</v>
       </c>
       <c r="B3" t="n">
-        <v>95652</v>
+        <v>91328</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>483</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518070</v>
+        <v>518028</v>
       </c>
       <c r="R3" t="n">
-        <v>6709176</v>
+        <v>6709071</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +873,11 @@
       </c>
       <c r="AE3" t="b">
         <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -996,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285619</v>
+        <v>121285634</v>
       </c>
       <c r="B5" t="n">
-        <v>91328</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,41 +1016,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>483</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518028</v>
+        <v>518077</v>
       </c>
       <c r="R5" t="n">
-        <v>6709071</v>
+        <v>6709154</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,11 +1092,6 @@
       </c>
       <c r="AE5" t="b">
         <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121285634</v>
+        <v>121285639</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
+        <v>95652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,25 +1230,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518077</v>
+        <v>518070</v>
       </c>
       <c r="R7" t="n">
-        <v>6709154</v>
+        <v>6709176</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121285632</v>
+        <v>121285620</v>
       </c>
       <c r="B8" t="n">
-        <v>5192</v>
+        <v>4769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518073</v>
+        <v>517983</v>
       </c>
       <c r="R8" t="n">
-        <v>6709135</v>
+        <v>6709000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121285630</v>
+        <v>121285632</v>
       </c>
       <c r="B9" t="n">
-        <v>8424</v>
+        <v>5192</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518018</v>
+        <v>518073</v>
       </c>
       <c r="R9" t="n">
-        <v>6709006</v>
+        <v>6709135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285620</v>
+        <v>121285630</v>
       </c>
       <c r="B10" t="n">
-        <v>4769</v>
+        <v>8424</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517983</v>
+        <v>518018</v>
       </c>
       <c r="R10" t="n">
-        <v>6709000</v>
+        <v>6709006</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285619</v>
+        <v>121285639</v>
       </c>
       <c r="B3" t="n">
-        <v>91328</v>
+        <v>95652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,41 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>483</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518028</v>
+        <v>518070</v>
       </c>
       <c r="R3" t="n">
-        <v>6709071</v>
+        <v>6709176</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,11 +870,6 @@
       </c>
       <c r="AE3" t="b">
         <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -897,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285638</v>
+        <v>121285634</v>
       </c>
       <c r="B4" t="n">
-        <v>95652</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518072</v>
+        <v>518077</v>
       </c>
       <c r="R4" t="n">
-        <v>6709135</v>
+        <v>6709154</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285634</v>
+        <v>121285638</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>95652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518077</v>
+        <v>518072</v>
       </c>
       <c r="R5" t="n">
-        <v>6709154</v>
+        <v>6709135</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121285633</v>
+        <v>121285619</v>
       </c>
       <c r="B6" t="n">
-        <v>97059</v>
+        <v>91328</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,38 +1115,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>483</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518077</v>
+        <v>518028</v>
       </c>
       <c r="R6" t="n">
-        <v>6709191</v>
+        <v>6709071</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,6 +1194,11 @@
       </c>
       <c r="AE6" t="b">
         <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121285639</v>
+        <v>121285633</v>
       </c>
       <c r="B7" t="n">
-        <v>95652</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,25 +1230,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518070</v>
+        <v>518077</v>
       </c>
       <c r="R7" t="n">
-        <v>6709176</v>
+        <v>6709191</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121285620</v>
+        <v>121285630</v>
       </c>
       <c r="B8" t="n">
-        <v>4769</v>
+        <v>8424</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517983</v>
+        <v>518018</v>
       </c>
       <c r="R8" t="n">
-        <v>6709000</v>
+        <v>6709006</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121285632</v>
+        <v>121285620</v>
       </c>
       <c r="B9" t="n">
-        <v>5192</v>
+        <v>4769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518073</v>
+        <v>517983</v>
       </c>
       <c r="R9" t="n">
-        <v>6709135</v>
+        <v>6709000</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285630</v>
+        <v>121285632</v>
       </c>
       <c r="B10" t="n">
-        <v>8424</v>
+        <v>5192</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518018</v>
+        <v>518073</v>
       </c>
       <c r="R10" t="n">
-        <v>6709006</v>
+        <v>6709135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121285631</v>
+        <v>121285633</v>
       </c>
       <c r="B2" t="n">
-        <v>91116</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518058</v>
+        <v>518077</v>
       </c>
       <c r="R2" t="n">
-        <v>6709102</v>
+        <v>6709191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285639</v>
+        <v>121285638</v>
       </c>
       <c r="B3" t="n">
         <v>95652</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518070</v>
+        <v>518072</v>
       </c>
       <c r="R3" t="n">
-        <v>6709176</v>
+        <v>6709135</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285634</v>
+        <v>121285631</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>91116</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518077</v>
+        <v>518058</v>
       </c>
       <c r="R4" t="n">
-        <v>6709154</v>
+        <v>6709102</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285638</v>
+        <v>121285634</v>
       </c>
       <c r="B5" t="n">
-        <v>95652</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518072</v>
+        <v>518077</v>
       </c>
       <c r="R5" t="n">
-        <v>6709135</v>
+        <v>6709154</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121285633</v>
+        <v>121285639</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
+        <v>95652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,25 +1230,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518077</v>
+        <v>518070</v>
       </c>
       <c r="R7" t="n">
-        <v>6709191</v>
+        <v>6709176</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121285633</v>
+        <v>121285634</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>97064</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>518077</v>
       </c>
       <c r="R2" t="n">
-        <v>6709191</v>
+        <v>6709154</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285638</v>
+        <v>121285633</v>
       </c>
       <c r="B3" t="n">
-        <v>95652</v>
+        <v>97064</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518072</v>
+        <v>518077</v>
       </c>
       <c r="R3" t="n">
-        <v>6709135</v>
+        <v>6709191</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285631</v>
+        <v>121285638</v>
       </c>
       <c r="B4" t="n">
-        <v>91116</v>
+        <v>95657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518058</v>
+        <v>518072</v>
       </c>
       <c r="R4" t="n">
-        <v>6709102</v>
+        <v>6709135</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285634</v>
+        <v>121285619</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>91333</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,38 +1008,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>483</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518077</v>
+        <v>518028</v>
       </c>
       <c r="R5" t="n">
-        <v>6709154</v>
+        <v>6709071</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,6 +1087,11 @@
       </c>
       <c r="AE5" t="b">
         <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1103,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121285619</v>
+        <v>121285639</v>
       </c>
       <c r="B6" t="n">
-        <v>91328</v>
+        <v>95657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,41 +1123,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>483</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518028</v>
+        <v>518070</v>
       </c>
       <c r="R6" t="n">
-        <v>6709071</v>
+        <v>6709176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,11 +1199,6 @@
       </c>
       <c r="AE6" t="b">
         <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121285639</v>
+        <v>121285631</v>
       </c>
       <c r="B7" t="n">
-        <v>95652</v>
+        <v>91121</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,25 +1230,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518070</v>
+        <v>518058</v>
       </c>
       <c r="R7" t="n">
-        <v>6709176</v>
+        <v>6709102</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1328,7 @@
         <v>121285630</v>
       </c>
       <c r="B8" t="n">
-        <v>8424</v>
+        <v>8425</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121285620</v>
+        <v>121285632</v>
       </c>
       <c r="B9" t="n">
-        <v>4769</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517983</v>
+        <v>518073</v>
       </c>
       <c r="R9" t="n">
-        <v>6709000</v>
+        <v>6709135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285632</v>
+        <v>121285620</v>
       </c>
       <c r="B10" t="n">
-        <v>5192</v>
+        <v>4770</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518073</v>
+        <v>517983</v>
       </c>
       <c r="R10" t="n">
-        <v>6709135</v>
+        <v>6709000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121285634</v>
+        <v>121285638</v>
       </c>
       <c r="B2" t="n">
-        <v>97064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518077</v>
+        <v>518072</v>
       </c>
       <c r="R2" t="n">
-        <v>6709154</v>
+        <v>6709135</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,44 +770,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285633</v>
+        <v>121285639</v>
       </c>
       <c r="B3" t="n">
-        <v>97064</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518077</v>
+        <v>518070</v>
       </c>
       <c r="R3" t="n">
-        <v>6709191</v>
+        <v>6709176</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,57 +872,55 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285638</v>
+        <v>121285619</v>
       </c>
       <c r="B4" t="n">
-        <v>95657</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>483</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518072</v>
+        <v>518028</v>
       </c>
       <c r="R4" t="n">
-        <v>6709135</v>
+        <v>6709071</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,6 +965,11 @@
       </c>
       <c r="AE4" t="b">
         <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -996,53 +989,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285619</v>
+        <v>121285631</v>
       </c>
       <c r="B5" t="n">
-        <v>91333</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>483</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518028</v>
+        <v>518058</v>
       </c>
       <c r="R5" t="n">
-        <v>6709071</v>
+        <v>6709102</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,11 +1072,6 @@
       </c>
       <c r="AE5" t="b">
         <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1111,50 +1091,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121285639</v>
+        <v>121285620</v>
       </c>
       <c r="B6" t="n">
-        <v>95657</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518070</v>
+        <v>517983</v>
       </c>
       <c r="R6" t="n">
-        <v>6709176</v>
+        <v>6709000</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,12 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1200,6 +1184,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1218,15 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121285631</v>
+        <v>121285627</v>
       </c>
       <c r="B7" t="n">
-        <v>91121</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,34 +1214,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518058</v>
+        <v>518083</v>
       </c>
       <c r="R7" t="n">
-        <v>6709102</v>
+        <v>6709204</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,6 +1296,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1325,15 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121285632</v>
+        <v>121285628</v>
       </c>
       <c r="B8" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518073</v>
+        <v>518081</v>
       </c>
       <c r="R8" t="n">
-        <v>6709135</v>
+        <v>6709203</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,15 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121285620</v>
+        <v>121285632</v>
       </c>
       <c r="B9" t="n">
-        <v>4770</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517983</v>
+        <v>518073</v>
       </c>
       <c r="R9" t="n">
-        <v>6709000</v>
+        <v>6709135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,12 +1501,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1552,7 +1532,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Erik Berg, Ursula Zinko</t>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1562,12 +1542,7 @@
         <v>121285630</v>
       </c>
       <c r="B10" t="n">
-        <v>8425</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,6 +1649,210 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121285633</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Repbäcken till Grycksbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>518077</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6709191</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Väg &amp; Miljö AB, Naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121285634</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Repbäcken till Grycksbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>518077</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6709154</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Väg &amp; Miljö AB, Naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ursula Zinko, Erik Berg, Björn Almkvist, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65254-2023 artfynd.xlsx
+++ b/artfynd/A 65254-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285638</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285639</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285619</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285631</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285620</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285627</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285628</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285632</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285630</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1750,6 +1800,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285633</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1852,8 +1907,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285634</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>